--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124468270</v>
+        <v>124468230</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573914</v>
+        <v>573911</v>
       </c>
       <c r="R2" t="n">
-        <v>6445061</v>
+        <v>6445053</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467878</v>
+        <v>124468040</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,39 +901,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573929</v>
+        <v>573953</v>
       </c>
       <c r="R4" t="n">
-        <v>6444991</v>
+        <v>6445004</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,12 +979,18 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1003,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468040</v>
+        <v>124467907</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,39 +1021,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573953</v>
+        <v>573904</v>
       </c>
       <c r="R5" t="n">
-        <v>6445004</v>
+        <v>6445014</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,18 +1099,12 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467963</v>
+        <v>124468270</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,38 +1135,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573945</v>
+        <v>573914</v>
       </c>
       <c r="R6" t="n">
-        <v>6445006</v>
+        <v>6445061</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1237,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467907</v>
+        <v>124468323</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,39 +1242,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1289,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573904</v>
+        <v>573925</v>
       </c>
       <c r="R7" t="n">
-        <v>6445014</v>
+        <v>6445060</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1333,6 +1318,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1351,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468323</v>
+        <v>124467963</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,31 +1349,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573925</v>
+        <v>573945</v>
       </c>
       <c r="R8" t="n">
-        <v>6445060</v>
+        <v>6445006</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,17 +1444,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468230</v>
+        <v>124467878</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,31 +1463,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573911</v>
+        <v>573929</v>
       </c>
       <c r="R9" t="n">
-        <v>6445053</v>
+        <v>6444991</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1546,7 +1547,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124468230</v>
+        <v>124468040</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573911</v>
+        <v>573953</v>
       </c>
       <c r="R2" t="n">
-        <v>6445053</v>
+        <v>6445004</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124468293</v>
+        <v>124468323</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -826,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573921</v>
+        <v>573925</v>
       </c>
       <c r="R3" t="n">
-        <v>6445056</v>
+        <v>6445060</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468040</v>
+        <v>124467878</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,39 +914,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573953</v>
+        <v>573929</v>
       </c>
       <c r="R4" t="n">
-        <v>6445004</v>
+        <v>6444991</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,18 +992,12 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,7 +1009,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1223,14 +1230,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468323</v>
+        <v>124468293</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1274,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573925</v>
+        <v>573921</v>
       </c>
       <c r="R7" t="n">
-        <v>6445060</v>
+        <v>6445056</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1330,17 +1337,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467963</v>
+        <v>124468230</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,38 +1356,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573945</v>
+        <v>573911</v>
       </c>
       <c r="R8" t="n">
-        <v>6445006</v>
+        <v>6445053</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467878</v>
+        <v>124467963</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1489,13 +1489,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573929</v>
+        <v>573945</v>
       </c>
       <c r="R9" t="n">
-        <v>6444991</v>
+        <v>6445006</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1547,6 +1546,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124468040</v>
+        <v>124468230</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573953</v>
+        <v>573911</v>
       </c>
       <c r="R2" t="n">
-        <v>6445004</v>
+        <v>6445053</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,11 +757,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -788,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124468323</v>
+        <v>124468040</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,29 +794,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -839,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573925</v>
+        <v>573953</v>
       </c>
       <c r="R3" t="n">
-        <v>6445060</v>
+        <v>6445004</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,6 +870,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467878</v>
+        <v>124468323</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,39 +914,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573929</v>
+        <v>573925</v>
       </c>
       <c r="R4" t="n">
-        <v>6444991</v>
+        <v>6445060</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,6 +990,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,17 +1002,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467907</v>
+        <v>124467963</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,13 +1047,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573904</v>
+        <v>573945</v>
       </c>
       <c r="R5" t="n">
-        <v>6445014</v>
+        <v>6445006</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,6 +1104,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1130,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468270</v>
+        <v>124467907</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,31 +1135,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573914</v>
+        <v>573904</v>
       </c>
       <c r="R6" t="n">
-        <v>6445061</v>
+        <v>6445014</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1219,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1337,17 +1337,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468230</v>
+        <v>124467878</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,31 +1356,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573911</v>
+        <v>573929</v>
       </c>
       <c r="R8" t="n">
-        <v>6445053</v>
+        <v>6444991</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1444,17 +1451,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467963</v>
+        <v>124468270</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,38 +1470,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573945</v>
+        <v>573914</v>
       </c>
       <c r="R9" t="n">
-        <v>6445006</v>
+        <v>6445061</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124468230</v>
+        <v>124468293</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573911</v>
+        <v>573921</v>
       </c>
       <c r="R2" t="n">
-        <v>6445053</v>
+        <v>6445056</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124468040</v>
+        <v>124467963</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +794,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,7 +826,6 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573953</v>
+        <v>573945</v>
       </c>
       <c r="R3" t="n">
-        <v>6445004</v>
+        <v>6445006</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,11 +869,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468323</v>
+        <v>124467907</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,31 +908,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573925</v>
+        <v>573904</v>
       </c>
       <c r="R4" t="n">
-        <v>6445060</v>
+        <v>6445014</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,7 +992,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467963</v>
+        <v>124468230</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,38 +1022,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573945</v>
+        <v>573911</v>
       </c>
       <c r="R5" t="n">
-        <v>6445006</v>
+        <v>6445053</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467907</v>
+        <v>124468323</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,39 +1129,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573904</v>
+        <v>573925</v>
       </c>
       <c r="R6" t="n">
-        <v>6445014</v>
+        <v>6445060</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,6 +1205,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468293</v>
+        <v>124467878</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,31 +1236,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573921</v>
+        <v>573929</v>
       </c>
       <c r="R7" t="n">
-        <v>6445056</v>
+        <v>6444991</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,7 +1320,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467878</v>
+        <v>124468270</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,39 +1350,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573929</v>
+        <v>573914</v>
       </c>
       <c r="R8" t="n">
-        <v>6444991</v>
+        <v>6445061</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,6 +1426,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468270</v>
+        <v>124468040</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,29 +1457,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1502,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573914</v>
+        <v>573953</v>
       </c>
       <c r="R9" t="n">
-        <v>6445061</v>
+        <v>6445004</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,6 +1533,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124468293</v>
+        <v>124468270</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573921</v>
+        <v>573914</v>
       </c>
       <c r="R2" t="n">
-        <v>6445056</v>
+        <v>6445061</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467963</v>
+        <v>124468230</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573945</v>
+        <v>573911</v>
       </c>
       <c r="R3" t="n">
-        <v>6445006</v>
+        <v>6445053</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467907</v>
+        <v>124468323</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,39 +901,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573904</v>
+        <v>573925</v>
       </c>
       <c r="R4" t="n">
-        <v>6445014</v>
+        <v>6445060</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468230</v>
+        <v>124467907</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,31 +1008,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573911</v>
+        <v>573904</v>
       </c>
       <c r="R5" t="n">
-        <v>6445053</v>
+        <v>6445014</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,7 +1092,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1117,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468323</v>
+        <v>124468040</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,29 +1122,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1161,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573925</v>
+        <v>573953</v>
       </c>
       <c r="R6" t="n">
-        <v>6445060</v>
+        <v>6445004</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1197,6 +1198,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1331,17 +1337,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468270</v>
+        <v>124467963</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,31 +1356,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1382,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573914</v>
+        <v>573945</v>
       </c>
       <c r="R8" t="n">
-        <v>6445061</v>
+        <v>6445006</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1445,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468040</v>
+        <v>124468293</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,37 +1470,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1497,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573953</v>
+        <v>573921</v>
       </c>
       <c r="R9" t="n">
-        <v>6445004</v>
+        <v>6445056</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,11 +1538,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468040</v>
+        <v>124467878</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,39 +1122,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573953</v>
+        <v>573929</v>
       </c>
       <c r="R6" t="n">
-        <v>6445004</v>
+        <v>6444991</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,18 +1200,12 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1223,17 +1217,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467878</v>
+        <v>124468040</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,39 +1236,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573929</v>
+        <v>573953</v>
       </c>
       <c r="R7" t="n">
-        <v>6444991</v>
+        <v>6445004</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1320,12 +1314,18 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467878</v>
+        <v>124468040</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,39 +1122,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573929</v>
+        <v>573953</v>
       </c>
       <c r="R6" t="n">
-        <v>6444991</v>
+        <v>6445004</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,12 +1200,18 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1217,17 +1223,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468040</v>
+        <v>124467878</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,39 +1242,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1276,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573953</v>
+        <v>573929</v>
       </c>
       <c r="R7" t="n">
-        <v>6445004</v>
+        <v>6444991</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1314,18 +1320,12 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124468270</v>
+        <v>124467907</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573914</v>
+        <v>573904</v>
       </c>
       <c r="R2" t="n">
-        <v>6445061</v>
+        <v>6445014</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124468230</v>
+        <v>124468040</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,29 +801,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -826,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573911</v>
+        <v>573953</v>
       </c>
       <c r="R3" t="n">
-        <v>6445053</v>
+        <v>6445004</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,6 +877,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468323</v>
+        <v>124468270</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -933,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573925</v>
+        <v>573914</v>
       </c>
       <c r="R4" t="n">
-        <v>6445060</v>
+        <v>6445061</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467907</v>
+        <v>124468323</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,39 +1028,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573904</v>
+        <v>573925</v>
       </c>
       <c r="R5" t="n">
-        <v>6445014</v>
+        <v>6445060</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,6 +1104,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468040</v>
+        <v>124468293</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,37 +1135,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1162,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573953</v>
+        <v>573921</v>
       </c>
       <c r="R6" t="n">
-        <v>6445004</v>
+        <v>6445056</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,11 +1203,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467878</v>
+        <v>124468230</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,39 +1242,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573929</v>
+        <v>573911</v>
       </c>
       <c r="R7" t="n">
-        <v>6444991</v>
+        <v>6445053</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,6 +1318,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1337,7 +1330,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1458,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468293</v>
+        <v>124467878</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,31 +1463,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573921</v>
+        <v>573929</v>
       </c>
       <c r="R9" t="n">
-        <v>6445056</v>
+        <v>6444991</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1546,7 +1547,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467907</v>
+        <v>124468040</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573904</v>
+        <v>573953</v>
       </c>
       <c r="R2" t="n">
-        <v>6445014</v>
+        <v>6445004</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,12 +765,18 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124468040</v>
+        <v>124467878</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +807,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573953</v>
+        <v>573929</v>
       </c>
       <c r="R3" t="n">
-        <v>6445004</v>
+        <v>6444991</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,18 +885,12 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468270</v>
+        <v>124467963</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573914</v>
+        <v>573945</v>
       </c>
       <c r="R4" t="n">
-        <v>6445061</v>
+        <v>6445006</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1016,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468323</v>
+        <v>124468293</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1060,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573925</v>
+        <v>573921</v>
       </c>
       <c r="R5" t="n">
-        <v>6445060</v>
+        <v>6445056</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468293</v>
+        <v>124467907</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,31 +1142,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573921</v>
+        <v>573904</v>
       </c>
       <c r="R6" t="n">
-        <v>6445056</v>
+        <v>6445014</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1211,7 +1226,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1337,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467963</v>
+        <v>124468323</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,38 +1363,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573945</v>
+        <v>573925</v>
       </c>
       <c r="R8" t="n">
-        <v>6445006</v>
+        <v>6445060</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467878</v>
+        <v>124468270</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,39 +1470,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573929</v>
+        <v>573914</v>
       </c>
       <c r="R9" t="n">
-        <v>6444991</v>
+        <v>6445061</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1547,6 +1546,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124468040</v>
+        <v>124467907</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573953</v>
+        <v>573904</v>
       </c>
       <c r="R2" t="n">
-        <v>6445004</v>
+        <v>6445014</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,18 +765,12 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467878</v>
+        <v>124468323</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,39 +801,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573929</v>
+        <v>573925</v>
       </c>
       <c r="R3" t="n">
-        <v>6444991</v>
+        <v>6445060</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467963</v>
+        <v>124468040</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,30 +908,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -953,6 +940,7 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573945</v>
+        <v>573953</v>
       </c>
       <c r="R4" t="n">
-        <v>6445006</v>
+        <v>6445004</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,6 +984,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468293</v>
+        <v>124468230</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1067,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573921</v>
+        <v>573911</v>
       </c>
       <c r="R5" t="n">
-        <v>6445056</v>
+        <v>6445053</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1130,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467907</v>
+        <v>124468293</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,39 +1135,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573904</v>
+        <v>573921</v>
       </c>
       <c r="R6" t="n">
-        <v>6445014</v>
+        <v>6445056</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,6 +1211,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1244,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468230</v>
+        <v>124467878</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,31 +1242,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573911</v>
+        <v>573929</v>
       </c>
       <c r="R7" t="n">
-        <v>6445053</v>
+        <v>6444991</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,7 +1326,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1351,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468323</v>
+        <v>124467963</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,31 +1356,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573925</v>
+        <v>573945</v>
       </c>
       <c r="R8" t="n">
-        <v>6445060</v>
+        <v>6445006</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467907</v>
+        <v>124468040</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573904</v>
+        <v>573953</v>
       </c>
       <c r="R2" t="n">
-        <v>6445014</v>
+        <v>6445004</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,12 +765,18 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124468323</v>
+        <v>124468270</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -833,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573925</v>
+        <v>573914</v>
       </c>
       <c r="R3" t="n">
-        <v>6445060</v>
+        <v>6445061</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468040</v>
+        <v>124467963</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,30 +914,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -940,7 +946,6 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573953</v>
+        <v>573945</v>
       </c>
       <c r="R4" t="n">
-        <v>6445004</v>
+        <v>6445006</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,11 +989,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468230</v>
+        <v>124468293</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573911</v>
+        <v>573921</v>
       </c>
       <c r="R5" t="n">
-        <v>6445053</v>
+        <v>6445056</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468293</v>
+        <v>124468323</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573921</v>
+        <v>573925</v>
       </c>
       <c r="R6" t="n">
-        <v>6445056</v>
+        <v>6445060</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467878</v>
+        <v>124467907</v>
       </c>
       <c r="B7" t="n">
         <v>57529</v>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573929</v>
+        <v>573904</v>
       </c>
       <c r="R7" t="n">
-        <v>6444991</v>
+        <v>6445014</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467963</v>
+        <v>124467878</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,21 +1360,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1382,12 +1382,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573945</v>
+        <v>573929</v>
       </c>
       <c r="R8" t="n">
-        <v>6445006</v>
+        <v>6444991</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468270</v>
+        <v>124468230</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573914</v>
+        <v>573911</v>
       </c>
       <c r="R9" t="n">
-        <v>6445061</v>
+        <v>6445053</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124468040</v>
+        <v>124468230</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573953</v>
+        <v>573911</v>
       </c>
       <c r="R2" t="n">
-        <v>6445004</v>
+        <v>6445053</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124468270</v>
+        <v>124468293</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -839,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573914</v>
+        <v>573921</v>
       </c>
       <c r="R3" t="n">
-        <v>6445061</v>
+        <v>6445056</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,17 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467963</v>
+        <v>124467907</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,12 +927,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573945</v>
+        <v>573904</v>
       </c>
       <c r="R4" t="n">
-        <v>6445006</v>
+        <v>6445014</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,7 +985,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468293</v>
+        <v>124467878</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,31 +1015,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573921</v>
+        <v>573929</v>
       </c>
       <c r="R5" t="n">
-        <v>6445056</v>
+        <v>6444991</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1099,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468323</v>
+        <v>124467963</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,31 +1129,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573925</v>
+        <v>573945</v>
       </c>
       <c r="R6" t="n">
-        <v>6445060</v>
+        <v>6445006</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467907</v>
+        <v>124468323</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,39 +1243,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573904</v>
+        <v>573925</v>
       </c>
       <c r="R7" t="n">
-        <v>6445014</v>
+        <v>6445060</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,6 +1319,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1337,17 +1331,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467878</v>
+        <v>124468270</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,39 +1350,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573929</v>
+        <v>573914</v>
       </c>
       <c r="R8" t="n">
-        <v>6444991</v>
+        <v>6445061</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,6 +1426,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1451,17 +1438,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468230</v>
+        <v>124468040</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,29 +1457,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1502,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573911</v>
+        <v>573953</v>
       </c>
       <c r="R9" t="n">
-        <v>6445053</v>
+        <v>6445004</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,6 +1533,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467907</v>
+        <v>124467878</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573904</v>
+        <v>573929</v>
       </c>
       <c r="R4" t="n">
-        <v>6445014</v>
+        <v>6444991</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467878</v>
+        <v>124467907</v>
       </c>
       <c r="B5" t="n">
         <v>57529</v>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573929</v>
+        <v>573904</v>
       </c>
       <c r="R5" t="n">
-        <v>6444991</v>
+        <v>6445014</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467878</v>
+        <v>124467907</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573929</v>
+        <v>573904</v>
       </c>
       <c r="R4" t="n">
-        <v>6444991</v>
+        <v>6445014</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467907</v>
+        <v>124467878</v>
       </c>
       <c r="B5" t="n">
         <v>57529</v>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573904</v>
+        <v>573929</v>
       </c>
       <c r="R5" t="n">
-        <v>6445014</v>
+        <v>6444991</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467963</v>
+        <v>124468323</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,38 +1129,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1168,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573945</v>
+        <v>573925</v>
       </c>
       <c r="R6" t="n">
-        <v>6445006</v>
+        <v>6445060</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,17 +1217,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468323</v>
+        <v>124467963</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,31 +1236,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573925</v>
+        <v>573945</v>
       </c>
       <c r="R7" t="n">
-        <v>6445060</v>
+        <v>6445006</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124468230</v>
+        <v>124468270</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573911</v>
+        <v>573914</v>
       </c>
       <c r="R2" t="n">
-        <v>6445053</v>
+        <v>6445061</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -882,17 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467907</v>
+        <v>124468230</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,39 +901,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573904</v>
+        <v>573911</v>
       </c>
       <c r="R4" t="n">
-        <v>6445014</v>
+        <v>6445053</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1003,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467878</v>
+        <v>124468323</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,39 +1008,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573929</v>
+        <v>573925</v>
       </c>
       <c r="R5" t="n">
-        <v>6444991</v>
+        <v>6445060</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,6 +1084,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1117,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468323</v>
+        <v>124467878</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,31 +1115,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573925</v>
+        <v>573929</v>
       </c>
       <c r="R6" t="n">
-        <v>6445060</v>
+        <v>6444991</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,7 +1199,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1217,17 +1210,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467963</v>
+        <v>124467907</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1233,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1262,12 +1255,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573945</v>
+        <v>573904</v>
       </c>
       <c r="R7" t="n">
-        <v>6445006</v>
+        <v>6445014</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1319,7 +1313,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1338,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468270</v>
+        <v>124467963</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,31 +1343,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573914</v>
+        <v>573945</v>
       </c>
       <c r="R8" t="n">
-        <v>6445061</v>
+        <v>6445006</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124468270</v>
+        <v>124468040</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573914</v>
+        <v>573953</v>
       </c>
       <c r="R2" t="n">
-        <v>6445061</v>
+        <v>6445004</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124468293</v>
+        <v>124467907</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,31 +807,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573921</v>
+        <v>573904</v>
       </c>
       <c r="R3" t="n">
-        <v>6445056</v>
+        <v>6445014</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +891,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468230</v>
+        <v>124468293</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -933,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573911</v>
+        <v>573921</v>
       </c>
       <c r="R4" t="n">
-        <v>6445053</v>
+        <v>6445056</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1103,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467878</v>
+        <v>124468270</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,39 +1135,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573929</v>
+        <v>573914</v>
       </c>
       <c r="R6" t="n">
-        <v>6444991</v>
+        <v>6445061</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,6 +1211,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1217,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467907</v>
+        <v>124467963</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1255,13 +1268,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573904</v>
+        <v>573945</v>
       </c>
       <c r="R7" t="n">
-        <v>6445014</v>
+        <v>6445006</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1313,6 +1325,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1331,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467963</v>
+        <v>124467878</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1360,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1369,12 +1382,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1382,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573945</v>
+        <v>573929</v>
       </c>
       <c r="R8" t="n">
-        <v>6445006</v>
+        <v>6444991</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1426,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1445,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468040</v>
+        <v>124468230</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,37 +1470,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1497,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573953</v>
+        <v>573911</v>
       </c>
       <c r="R9" t="n">
-        <v>6445004</v>
+        <v>6445053</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,11 +1538,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124468040</v>
+        <v>124467907</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573953</v>
+        <v>573904</v>
       </c>
       <c r="R2" t="n">
-        <v>6445004</v>
+        <v>6445014</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,18 +765,12 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467907</v>
+        <v>124468230</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,39 +801,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573904</v>
+        <v>573911</v>
       </c>
       <c r="R3" t="n">
-        <v>6445014</v>
+        <v>6445053</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468293</v>
+        <v>124467878</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +908,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573921</v>
+        <v>573929</v>
       </c>
       <c r="R4" t="n">
-        <v>6445056</v>
+        <v>6444991</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,7 +992,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468323</v>
+        <v>124468293</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1060,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573925</v>
+        <v>573921</v>
       </c>
       <c r="R5" t="n">
-        <v>6445060</v>
+        <v>6445056</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1230,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467963</v>
+        <v>124468323</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,38 +1236,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573945</v>
+        <v>573925</v>
       </c>
       <c r="R7" t="n">
-        <v>6445006</v>
+        <v>6445060</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1344,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467878</v>
+        <v>124468040</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,39 +1343,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573929</v>
+        <v>573953</v>
       </c>
       <c r="R8" t="n">
-        <v>6444991</v>
+        <v>6445004</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1434,12 +1421,18 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468230</v>
+        <v>124467963</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,31 +1463,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573911</v>
+        <v>573945</v>
       </c>
       <c r="R9" t="n">
-        <v>6445053</v>
+        <v>6445006</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467907</v>
+        <v>124468323</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573904</v>
+        <v>573925</v>
       </c>
       <c r="R2" t="n">
-        <v>6445014</v>
+        <v>6445060</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124468230</v>
+        <v>124467878</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,31 +794,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573911</v>
+        <v>573929</v>
       </c>
       <c r="R3" t="n">
-        <v>6445053</v>
+        <v>6444991</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467878</v>
+        <v>124468230</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,39 +908,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573929</v>
+        <v>573911</v>
       </c>
       <c r="R4" t="n">
-        <v>6444991</v>
+        <v>6445053</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,6 +984,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468293</v>
+        <v>124467963</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,31 +1015,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573921</v>
+        <v>573945</v>
       </c>
       <c r="R5" t="n">
-        <v>6445056</v>
+        <v>6445006</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468270</v>
+        <v>124468293</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573914</v>
+        <v>573921</v>
       </c>
       <c r="R6" t="n">
-        <v>6445061</v>
+        <v>6445056</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468323</v>
+        <v>124468040</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,29 +1236,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1268,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573925</v>
+        <v>573953</v>
       </c>
       <c r="R7" t="n">
-        <v>6445060</v>
+        <v>6445004</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,6 +1312,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468040</v>
+        <v>124468270</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,37 +1356,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1383,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573953</v>
+        <v>573914</v>
       </c>
       <c r="R8" t="n">
-        <v>6445004</v>
+        <v>6445061</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,11 +1424,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467963</v>
+        <v>124467907</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1489,12 +1489,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573945</v>
+        <v>573904</v>
       </c>
       <c r="R9" t="n">
-        <v>6445006</v>
+        <v>6445014</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1546,7 +1547,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13109-2025 artfynd.xlsx
+++ b/artfynd/A 13109-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467878</v>
+        <v>124467963</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,13 +820,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573929</v>
+        <v>573945</v>
       </c>
       <c r="R3" t="n">
-        <v>6444991</v>
+        <v>6445006</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468230</v>
+        <v>124468293</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573911</v>
+        <v>573921</v>
       </c>
       <c r="R4" t="n">
-        <v>6445053</v>
+        <v>6445056</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467963</v>
+        <v>124467878</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1041,12 +1041,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573945</v>
+        <v>573929</v>
       </c>
       <c r="R5" t="n">
-        <v>6445006</v>
+        <v>6444991</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,7 +1099,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468293</v>
+        <v>124468230</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573921</v>
+        <v>573911</v>
       </c>
       <c r="R6" t="n">
-        <v>6445056</v>
+        <v>6445053</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468040</v>
+        <v>124468270</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,37 +1236,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1276,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573953</v>
+        <v>573914</v>
       </c>
       <c r="R7" t="n">
-        <v>6445004</v>
+        <v>6445061</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,11 +1304,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468270</v>
+        <v>124467907</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,31 +1343,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573914</v>
+        <v>573904</v>
       </c>
       <c r="R8" t="n">
-        <v>6445061</v>
+        <v>6445014</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,7 +1427,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1451,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467907</v>
+        <v>124468040</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,39 +1457,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573904</v>
+        <v>573953</v>
       </c>
       <c r="R9" t="n">
-        <v>6445014</v>
+        <v>6445004</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1541,12 +1535,18 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer över hela våtmarksområdet, ca 4000 m2</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
